--- a/output/BOINTEC.new.summary_ 4x4 _ 100-25-75-0 .xlsx
+++ b/output/BOINTEC.new.summary_ 4x4 _ 100-25-75-0 .xlsx
@@ -1719,10 +1719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
@@ -1731,57 +1731,57 @@
         <v>0.6</v>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>8.6</v>
+        <v>15.2</v>
       </c>
       <c r="I22" t="n">
-        <v>10.4</v>
+        <v>8.5</v>
       </c>
       <c r="J22" t="n">
-        <v>7.18</v>
+        <v>3.82</v>
       </c>
       <c r="K22" t="n">
-        <v>31.6</v>
+        <v>16.2</v>
       </c>
       <c r="L22" t="n">
-        <v>7.7</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
-        <v>5.3</v>
+        <v>1.98</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="P22" t="n">
-        <v>0.56</v>
+        <v>0.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -1790,57 +1790,57 @@
         <v>0.6</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>3.3</v>
+        <v>12.6</v>
       </c>
       <c r="I23" t="n">
-        <v>7.8</v>
+        <v>10.3</v>
       </c>
       <c r="J23" t="n">
-        <v>5.4</v>
+        <v>4.12</v>
       </c>
       <c r="K23" t="n">
-        <v>8.5</v>
+        <v>24.8</v>
       </c>
       <c r="L23" t="n">
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
       <c r="M23" t="n">
-        <v>6.65</v>
+        <v>3.44</v>
       </c>
       <c r="N23" t="n">
-        <v>21.8</v>
+        <v>7.1</v>
       </c>
       <c r="O23" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="P23" t="n">
-        <v>4.51</v>
+        <v>0.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.33</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -1849,57 +1849,57 @@
         <v>0.6</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="I24" t="n">
-        <v>6.1</v>
+        <v>10.7</v>
       </c>
       <c r="J24" t="n">
-        <v>4.21</v>
+        <v>3.93</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1</v>
+        <v>6.7</v>
       </c>
       <c r="L24" t="n">
-        <v>7.5</v>
+        <v>9.7</v>
       </c>
       <c r="M24" t="n">
-        <v>5.17</v>
+        <v>4.09</v>
       </c>
       <c r="N24" t="n">
-        <v>6.5</v>
+        <v>25.6</v>
       </c>
       <c r="O24" t="n">
-        <v>10.2</v>
+        <v>7.9</v>
       </c>
       <c r="P24" t="n">
-        <v>7.08</v>
+        <v>3.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>18.2</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>4.31</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B25" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C25" t="n">
         <v>3</v>
@@ -1908,54 +1908,54 @@
         <v>0.6</v>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="I25" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="J25" t="n">
         <v>3.56</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>2.99</v>
       </c>
       <c r="N25" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>7.3</v>
+        <v>11.2</v>
       </c>
       <c r="P25" t="n">
-        <v>5.01</v>
+        <v>4.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.2</v>
+        <v>9.3</v>
       </c>
       <c r="R25" t="n">
-        <v>9.2</v>
+        <v>8.5</v>
       </c>
       <c r="S25" t="n">
-        <v>6.2</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" t="n">
         <v>48</v>
@@ -1976,34 +1976,34 @@
         <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>15.2</v>
+        <v>18.6</v>
       </c>
       <c r="I26" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="J26" t="n">
-        <v>3.82</v>
+        <v>3.27</v>
       </c>
       <c r="K26" t="n">
-        <v>16.2</v>
+        <v>19.6</v>
       </c>
       <c r="L26" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="M26" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>12.1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P26" t="n">
-        <v>0.15</v>
+        <v>0.07</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" t="n">
         <v>48</v>
@@ -2035,45 +2035,45 @@
         <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="I27" t="n">
-        <v>10.3</v>
+        <v>9.7</v>
       </c>
       <c r="J27" t="n">
-        <v>4.12</v>
+        <v>3.67</v>
       </c>
       <c r="K27" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="L27" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.44</v>
+        <v>2.79</v>
       </c>
       <c r="N27" t="n">
-        <v>7.1</v>
+        <v>10.7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="P27" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.6</v>
+        <v>6.9</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="S27" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28" t="n">
         <v>48</v>
@@ -2094,45 +2094,45 @@
         <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>5.7</v>
+        <v>8.9</v>
       </c>
       <c r="I28" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="J28" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="K28" t="n">
-        <v>6.7</v>
+        <v>9.3</v>
       </c>
       <c r="L28" t="n">
-        <v>9.7</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>4.09</v>
+        <v>3.44</v>
       </c>
       <c r="N28" t="n">
-        <v>25.6</v>
+        <v>26.2</v>
       </c>
       <c r="O28" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="P28" t="n">
-        <v>3.41</v>
+        <v>3.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B29" t="n">
         <v>48</v>
@@ -2153,40 +2153,40 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="I29" t="n">
-        <v>9.6</v>
+        <v>10.9</v>
       </c>
       <c r="J29" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="K29" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="L29" t="n">
-        <v>8.6</v>
+        <v>10.2</v>
       </c>
       <c r="M29" t="n">
-        <v>2.99</v>
+        <v>3.13</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
-        <v>11.2</v>
+        <v>12.7</v>
       </c>
       <c r="P29" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.3</v>
+        <v>10.2</v>
       </c>
       <c r="R29" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="S29" t="n">
-        <v>3.22</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="30">
@@ -2194,7 +2194,7 @@
         <v>19</v>
       </c>
       <c r="B30" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C30" t="n">
         <v>3</v>
@@ -2203,49 +2203,49 @@
         <v>0.6</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>8.6</v>
+        <v>34.3</v>
       </c>
       <c r="I30" t="n">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
       <c r="J30" t="n">
-        <v>7.32</v>
+        <v>3.98</v>
       </c>
       <c r="K30" t="n">
-        <v>16.6</v>
+        <v>11.8</v>
       </c>
       <c r="L30" t="n">
-        <v>6.7</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
-        <v>4.59</v>
+        <v>0.98</v>
       </c>
       <c r="N30" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O30" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="P30" t="n">
-        <v>0.38</v>
+        <v>0.09</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2253,7 +2253,7 @@
         <v>19</v>
       </c>
       <c r="B31" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
@@ -2262,49 +2262,49 @@
         <v>0.6</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="I31" t="n">
-        <v>8.6</v>
+        <v>9.7</v>
       </c>
       <c r="J31" t="n">
-        <v>5.34</v>
+        <v>3.92</v>
       </c>
       <c r="K31" t="n">
-        <v>27.8</v>
+        <v>25.4</v>
       </c>
       <c r="L31" t="n">
-        <v>10.6</v>
+        <v>7.9</v>
       </c>
       <c r="M31" t="n">
-        <v>7.15</v>
+        <v>3.59</v>
       </c>
       <c r="N31" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="O31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="Q31" t="n">
         <v>2.6</v>
       </c>
-      <c r="P31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.7</v>
-      </c>
       <c r="R31" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="32">
@@ -2312,7 +2312,7 @@
         <v>19</v>
       </c>
       <c r="B32" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C32" t="n">
         <v>3</v>
@@ -2321,49 +2321,49 @@
         <v>0.6</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="I32" t="n">
-        <v>7.1</v>
+        <v>10.7</v>
       </c>
       <c r="J32" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="K32" t="n">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="L32" t="n">
-        <v>9.1</v>
+        <v>10.4</v>
       </c>
       <c r="M32" t="n">
-        <v>5.84</v>
+        <v>4.39</v>
       </c>
       <c r="N32" t="n">
-        <v>32.1</v>
+        <v>7.3</v>
       </c>
       <c r="O32" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="P32" t="n">
-        <v>7.11</v>
+        <v>3.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
       <c r="R32" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S32" t="n">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="33">
@@ -2371,7 +2371,7 @@
         <v>19</v>
       </c>
       <c r="B33" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C33" t="n">
         <v>3</v>
@@ -2380,57 +2380,57 @@
         <v>0.6</v>
       </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="I33" t="n">
-        <v>6.1</v>
+        <v>10.1</v>
       </c>
       <c r="J33" t="n">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="L33" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="M33" t="n">
-        <v>2.95</v>
+        <v>3.33</v>
       </c>
       <c r="N33" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="O33" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="P33" t="n">
-        <v>5.87</v>
+        <v>4.13</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="R33" t="n">
-        <v>9.8</v>
+        <v>7.7</v>
       </c>
       <c r="S33" t="n">
-        <v>5.98</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B34" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C34" t="n">
         <v>3</v>
@@ -2439,43 +2439,43 @@
         <v>0.6</v>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>18.6</v>
+        <v>39.4</v>
       </c>
       <c r="I34" t="n">
-        <v>7.4</v>
+        <v>11.4</v>
       </c>
       <c r="J34" t="n">
-        <v>3.27</v>
+        <v>7.49</v>
       </c>
       <c r="K34" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="L34" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="M34" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="N34" t="n">
-        <v>12.1</v>
+        <v>1.4</v>
       </c>
       <c r="O34" t="n">
         <v>0.2</v>
       </c>
       <c r="P34" t="n">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>1.2</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C35" t="n">
         <v>3</v>
@@ -2498,57 +2498,57 @@
         <v>0.6</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
         <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>15.6</v>
+        <v>6.8</v>
       </c>
       <c r="I35" t="n">
-        <v>9.7</v>
+        <v>8.4</v>
       </c>
       <c r="J35" t="n">
-        <v>3.67</v>
+        <v>5.23</v>
       </c>
       <c r="K35" t="n">
-        <v>25.1</v>
+        <v>32.2</v>
       </c>
       <c r="L35" t="n">
-        <v>6.1</v>
+        <v>10.7</v>
       </c>
       <c r="M35" t="n">
-        <v>2.79</v>
+        <v>7.05</v>
       </c>
       <c r="N35" t="n">
-        <v>10.7</v>
+        <v>5.4</v>
       </c>
       <c r="O35" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="P35" t="n">
-        <v>0.72</v>
+        <v>1.57</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.9</v>
+        <v>0.8</v>
       </c>
       <c r="R35" t="n">
         <v>0.2</v>
       </c>
       <c r="S35" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B36" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C36" t="n">
         <v>3</v>
@@ -2557,57 +2557,57 @@
         <v>0.6</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="I36" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="J36" t="n">
-        <v>3.86</v>
+        <v>4.34</v>
       </c>
       <c r="K36" t="n">
-        <v>9.3</v>
+        <v>2.6</v>
       </c>
       <c r="L36" t="n">
-        <v>8.4</v>
+        <v>10.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.44</v>
+        <v>6.59</v>
       </c>
       <c r="N36" t="n">
-        <v>26.2</v>
+        <v>4.8</v>
       </c>
       <c r="O36" t="n">
-        <v>7.5</v>
+        <v>9.9</v>
       </c>
       <c r="P36" t="n">
-        <v>3.18</v>
+        <v>6.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0.58</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B37" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C37" t="n">
         <v>3</v>
@@ -2616,49 +2616,49 @@
         <v>0.6</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="I37" t="n">
-        <v>10.9</v>
+        <v>6.1</v>
       </c>
       <c r="J37" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="K37" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="L37" t="n">
-        <v>10.2</v>
+        <v>5.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.13</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="O37" t="n">
-        <v>12.7</v>
+        <v>10.4</v>
       </c>
       <c r="P37" t="n">
-        <v>4.46</v>
+        <v>6.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>10.2</v>
+        <v>2.1</v>
       </c>
       <c r="R37" t="n">
-        <v>8.4</v>
+        <v>10.1</v>
       </c>
       <c r="S37" t="n">
-        <v>2.97</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="38">
@@ -2666,7 +2666,7 @@
         <v>20</v>
       </c>
       <c r="B38" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C38" t="n">
         <v>3</v>
@@ -2675,49 +2675,49 @@
         <v>0.6</v>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>9.2</v>
+        <v>38.3</v>
       </c>
       <c r="I38" t="n">
-        <v>10.1</v>
+        <v>7.8</v>
       </c>
       <c r="J38" t="n">
-        <v>6.56</v>
+        <v>3.42</v>
       </c>
       <c r="K38" t="n">
         <v>16.2</v>
       </c>
       <c r="L38" t="n">
-        <v>5.4</v>
+        <v>1.6</v>
       </c>
       <c r="M38" t="n">
-        <v>3.64</v>
+        <v>0.76</v>
       </c>
       <c r="N38" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="O38" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="P38" t="n">
-        <v>0.22</v>
+        <v>0.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>10.6</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2725,7 +2725,7 @@
         <v>20</v>
       </c>
       <c r="B39" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C39" t="n">
         <v>3</v>
@@ -2734,49 +2734,49 @@
         <v>0.6</v>
       </c>
       <c r="E39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
         <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>8.2</v>
+        <v>18.2</v>
       </c>
       <c r="I39" t="n">
-        <v>9.7</v>
+        <v>9.4</v>
       </c>
       <c r="J39" t="n">
-        <v>5.7</v>
+        <v>3.61</v>
       </c>
       <c r="K39" t="n">
-        <v>27.4</v>
+        <v>25.4</v>
       </c>
       <c r="L39" t="n">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="M39" t="n">
-        <v>6.07</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>7.8</v>
+        <v>10.7</v>
       </c>
       <c r="O39" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="P39" t="n">
-        <v>1.68</v>
+        <v>0.71</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="R39" t="n">
         <v>0.1</v>
       </c>
       <c r="S39" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="40">
@@ -2784,7 +2784,7 @@
         <v>20</v>
       </c>
       <c r="B40" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C40" t="n">
         <v>3</v>
@@ -2793,49 +2793,49 @@
         <v>0.6</v>
       </c>
       <c r="E40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>2.8</v>
+        <v>9.3</v>
       </c>
       <c r="I40" t="n">
-        <v>8.2</v>
+        <v>11.6</v>
       </c>
       <c r="J40" t="n">
-        <v>4.59</v>
+        <v>3.82</v>
       </c>
       <c r="K40" t="n">
-        <v>4.8</v>
+        <v>9.1</v>
       </c>
       <c r="L40" t="n">
-        <v>9</v>
+        <v>9.3</v>
       </c>
       <c r="M40" t="n">
-        <v>5.64</v>
+        <v>3.82</v>
       </c>
       <c r="N40" t="n">
-        <v>29.9</v>
+        <v>10.1</v>
       </c>
       <c r="O40" t="n">
-        <v>10.3</v>
+        <v>7</v>
       </c>
       <c r="P40" t="n">
-        <v>6.44</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
-        <v>1.26</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="41">
@@ -2843,7 +2843,7 @@
         <v>20</v>
       </c>
       <c r="B41" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C41" t="n">
         <v>3</v>
@@ -2852,57 +2852,57 @@
         <v>0.6</v>
       </c>
       <c r="E41" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="I41" t="n">
-        <v>6.5</v>
+        <v>10.7</v>
       </c>
       <c r="J41" t="n">
-        <v>3.68</v>
+        <v>3.48</v>
       </c>
       <c r="K41" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="L41" t="n">
-        <v>6.1</v>
+        <v>10.4</v>
       </c>
       <c r="M41" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
-        <v>11.2</v>
+        <v>13.5</v>
       </c>
       <c r="P41" t="n">
-        <v>6.53</v>
+        <v>4.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="R41" t="n">
-        <v>9.7</v>
+        <v>8.2</v>
       </c>
       <c r="S41" t="n">
-        <v>5.61</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B42" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C42" t="n">
         <v>3</v>
@@ -2911,57 +2911,57 @@
         <v>0.6</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
         <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>8.5</v>
+        <v>40.6</v>
       </c>
       <c r="I42" t="n">
-        <v>7.7</v>
+        <v>10.6</v>
       </c>
       <c r="J42" t="n">
-        <v>3.51</v>
+        <v>6.83</v>
       </c>
       <c r="K42" t="n">
-        <v>12.4</v>
+        <v>10.8</v>
       </c>
       <c r="L42" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="M42" t="n">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="N42" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P42" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B43" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C43" t="n">
         <v>3</v>
@@ -2970,57 +2970,57 @@
         <v>0.6</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
         <v>3</v>
       </c>
       <c r="H43" t="n">
-        <v>6.6</v>
+        <v>10.1</v>
       </c>
       <c r="I43" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J43" t="n">
-        <v>3.99</v>
+        <v>5.36</v>
       </c>
       <c r="K43" t="n">
-        <v>23.6</v>
+        <v>31.4</v>
       </c>
       <c r="L43" t="n">
-        <v>7.1</v>
+        <v>9.8</v>
       </c>
       <c r="M43" t="n">
-        <v>3.19</v>
+        <v>6.37</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O43" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="P43" t="n">
-        <v>0.56</v>
+        <v>1.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="S43" t="n">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B44" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C44" t="n">
         <v>3</v>
@@ -3029,57 +3029,57 @@
         <v>0.6</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
         <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>8.9</v>
+        <v>8.3</v>
       </c>
       <c r="J44" t="n">
-        <v>3.83</v>
+        <v>4.54</v>
       </c>
       <c r="K44" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="L44" t="n">
-        <v>9.1</v>
+        <v>9.7</v>
       </c>
       <c r="M44" t="n">
-        <v>4.01</v>
+        <v>6.06</v>
       </c>
       <c r="N44" t="n">
-        <v>36.9</v>
+        <v>6.9</v>
       </c>
       <c r="O44" t="n">
-        <v>11.1</v>
+        <v>9.5</v>
       </c>
       <c r="P44" t="n">
-        <v>4.87</v>
+        <v>6</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="S44" t="n">
-        <v>0.76</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B45" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C45" t="n">
         <v>3</v>
@@ -3088,49 +3088,49 @@
         <v>0.6</v>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="J45" t="n">
-        <v>3.43</v>
+        <v>3.76</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="L45" t="n">
-        <v>9.2</v>
+        <v>6.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.92</v>
+        <v>3.76</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O45" t="n">
-        <v>10.8</v>
+        <v>12.7</v>
       </c>
       <c r="P45" t="n">
-        <v>4.66</v>
+        <v>7.29</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="R45" t="n">
-        <v>12</v>
+        <v>8.8</v>
       </c>
       <c r="S45" t="n">
-        <v>5.1</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="46">
@@ -3138,7 +3138,7 @@
         <v>21</v>
       </c>
       <c r="B46" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C46" t="n">
         <v>3</v>
@@ -3147,49 +3147,49 @@
         <v>0.6</v>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
         <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>6.7</v>
+        <v>33.5</v>
       </c>
       <c r="I46" t="n">
-        <v>10.1</v>
+        <v>8.1</v>
       </c>
       <c r="J46" t="n">
-        <v>6.69</v>
+        <v>3.59</v>
       </c>
       <c r="K46" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="L46" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.73</v>
+        <v>0.74</v>
       </c>
       <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="n">
         <v>0.1</v>
       </c>
-      <c r="O46" t="n">
-        <v>0.3</v>
-      </c>
       <c r="P46" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3197,7 +3197,7 @@
         <v>21</v>
       </c>
       <c r="B47" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C47" t="n">
         <v>3</v>
@@ -3206,49 +3206,49 @@
         <v>0.6</v>
       </c>
       <c r="E47" t="n">
+        <v>6</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>9.8</v>
+      </c>
+      <c r="I47" t="n">
         <v>9</v>
       </c>
-      <c r="F47" t="n">
-        <v>4</v>
-      </c>
-      <c r="G47" t="n">
-        <v>3</v>
-      </c>
-      <c r="H47" t="n">
-        <v>4</v>
-      </c>
-      <c r="I47" t="n">
-        <v>8.8</v>
-      </c>
       <c r="J47" t="n">
-        <v>5.74</v>
+        <v>3.93</v>
       </c>
       <c r="K47" t="n">
-        <v>30</v>
+        <v>23.8</v>
       </c>
       <c r="L47" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="M47" t="n">
-        <v>6.5</v>
+        <v>3.09</v>
       </c>
       <c r="N47" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O47" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="P47" t="n">
-        <v>1.47</v>
+        <v>0.69</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="R47" t="n">
         <v>0.1</v>
       </c>
       <c r="S47" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="48">
@@ -3256,7 +3256,7 @@
         <v>21</v>
       </c>
       <c r="B48" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C48" t="n">
         <v>3</v>
@@ -3265,49 +3265,49 @@
         <v>0.6</v>
       </c>
       <c r="E48" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
         <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="I48" t="n">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
       <c r="J48" t="n">
-        <v>4.53</v>
+        <v>3.88</v>
       </c>
       <c r="K48" t="n">
-        <v>2.9</v>
+        <v>8.3</v>
       </c>
       <c r="L48" t="n">
-        <v>8.4</v>
+        <v>9.8</v>
       </c>
       <c r="M48" t="n">
-        <v>5.52</v>
+        <v>4.26</v>
       </c>
       <c r="N48" t="n">
-        <v>36</v>
+        <v>12.2</v>
       </c>
       <c r="O48" t="n">
-        <v>12.2</v>
+        <v>9.7</v>
       </c>
       <c r="P48" t="n">
-        <v>7.93</v>
+        <v>4.28</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="S48" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="49">
@@ -3315,7 +3315,7 @@
         <v>21</v>
       </c>
       <c r="B49" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C49" t="n">
         <v>3</v>
@@ -3324,57 +3324,57 @@
         <v>0.6</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I49" t="n">
-        <v>5.7</v>
+        <v>8.1</v>
       </c>
       <c r="J49" t="n">
-        <v>3.72</v>
+        <v>3.46</v>
       </c>
       <c r="K49" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="L49" t="n">
-        <v>6.6</v>
+        <v>9.7</v>
       </c>
       <c r="M49" t="n">
-        <v>4.27</v>
+        <v>4.11</v>
       </c>
       <c r="N49" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="O49" t="n">
-        <v>8.5</v>
+        <v>11.6</v>
       </c>
       <c r="P49" t="n">
-        <v>5.47</v>
+        <v>4.96</v>
       </c>
       <c r="Q49" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="R49" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S49" t="n">
-        <v>7.85</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B50" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C50" t="n">
         <v>3</v>
@@ -3383,7 +3383,7 @@
         <v>0.6</v>
       </c>
       <c r="E50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F50" t="n">
         <v>5</v>
@@ -3392,48 +3392,48 @@
         <v>4</v>
       </c>
       <c r="H50" t="n">
-        <v>34.3</v>
+        <v>40.3</v>
       </c>
       <c r="I50" t="n">
-        <v>8.9</v>
+        <v>10.6</v>
       </c>
       <c r="J50" t="n">
-        <v>3.98</v>
+        <v>6.93</v>
       </c>
       <c r="K50" t="n">
-        <v>11.8</v>
+        <v>8.3</v>
       </c>
       <c r="L50" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="M50" t="n">
-        <v>0.98</v>
+        <v>1.78</v>
       </c>
       <c r="N50" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="O50" t="n">
         <v>0.2</v>
       </c>
       <c r="P50" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B51" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C51" t="n">
         <v>3</v>
@@ -3442,7 +3442,7 @@
         <v>0.6</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -3451,48 +3451,48 @@
         <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>14.6</v>
+        <v>5.5</v>
       </c>
       <c r="I51" t="n">
-        <v>9.7</v>
+        <v>8.5</v>
       </c>
       <c r="J51" t="n">
-        <v>3.92</v>
+        <v>5.54</v>
       </c>
       <c r="K51" t="n">
-        <v>25.4</v>
+        <v>29.8</v>
       </c>
       <c r="L51" t="n">
-        <v>7.9</v>
+        <v>9.2</v>
       </c>
       <c r="M51" t="n">
-        <v>3.59</v>
+        <v>6.04</v>
       </c>
       <c r="N51" t="n">
-        <v>7.3</v>
+        <v>5.9</v>
       </c>
       <c r="O51" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="P51" t="n">
-        <v>0.81</v>
+        <v>1.39</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="R51" t="n">
         <v>0.1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B52" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C52" t="n">
         <v>3</v>
@@ -3501,7 +3501,7 @@
         <v>0.6</v>
       </c>
       <c r="E52" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F52" t="n">
         <v>5</v>
@@ -3510,48 +3510,48 @@
         <v>2</v>
       </c>
       <c r="H52" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="I52" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J52" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L52" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>6</v>
+      </c>
+      <c r="N52" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O52" t="n">
         <v>10.7</v>
       </c>
-      <c r="J52" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K52" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="M52" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="N52" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O52" t="n">
-        <v>7.2</v>
-      </c>
       <c r="P52" t="n">
-        <v>3.18</v>
+        <v>7.02</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="R52" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="S52" t="n">
-        <v>1.23</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B53" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C53" t="n">
         <v>3</v>
@@ -3560,7 +3560,7 @@
         <v>0.6</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
@@ -3569,40 +3569,40 @@
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="I53" t="n">
-        <v>10.1</v>
+        <v>5.7</v>
       </c>
       <c r="J53" t="n">
-        <v>3.65</v>
+        <v>3.71</v>
       </c>
       <c r="K53" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="L53" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="M53" t="n">
-        <v>3.33</v>
+        <v>4.93</v>
       </c>
       <c r="N53" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="O53" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="P53" t="n">
-        <v>4.13</v>
+        <v>6.56</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="R53" t="n">
-        <v>7.7</v>
+        <v>12.5</v>
       </c>
       <c r="S53" t="n">
-        <v>2.92</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="54">
@@ -3610,7 +3610,7 @@
         <v>19</v>
       </c>
       <c r="B54" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C54" t="n">
         <v>3</v>
@@ -3619,49 +3619,49 @@
         <v>0.6</v>
       </c>
       <c r="E54" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G54" t="n">
         <v>4</v>
       </c>
       <c r="H54" t="n">
-        <v>39.4</v>
+        <v>9.1</v>
       </c>
       <c r="I54" t="n">
-        <v>11.4</v>
+        <v>8.1</v>
       </c>
       <c r="J54" t="n">
-        <v>7.49</v>
+        <v>3.6</v>
       </c>
       <c r="K54" t="n">
-        <v>9.6</v>
+        <v>13.1</v>
       </c>
       <c r="L54" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="M54" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="N54" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="P54" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R54" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="55">
@@ -3669,7 +3669,7 @@
         <v>19</v>
       </c>
       <c r="B55" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C55" t="n">
         <v>3</v>
@@ -3678,49 +3678,49 @@
         <v>0.6</v>
       </c>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G55" t="n">
         <v>3</v>
       </c>
       <c r="H55" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="I55" t="n">
-        <v>8.4</v>
+        <v>10.4</v>
       </c>
       <c r="J55" t="n">
-        <v>5.23</v>
+        <v>4.14</v>
       </c>
       <c r="K55" t="n">
-        <v>32.2</v>
+        <v>20.4</v>
       </c>
       <c r="L55" t="n">
-        <v>10.7</v>
+        <v>7.4</v>
       </c>
       <c r="M55" t="n">
-        <v>7.05</v>
+        <v>3.36</v>
       </c>
       <c r="N55" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="O55" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="P55" t="n">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="R55" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="S55" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="56">
@@ -3728,7 +3728,7 @@
         <v>19</v>
       </c>
       <c r="B56" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C56" t="n">
         <v>3</v>
@@ -3737,49 +3737,49 @@
         <v>0.6</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
         <v>2</v>
       </c>
       <c r="H56" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I56" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K56" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L56" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N56" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="O56" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="R56" t="n">
         <v>2.9</v>
       </c>
-      <c r="I56" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J56" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L56" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M56" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="N56" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O56" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="P56" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R56" t="n">
-        <v>4.3</v>
-      </c>
       <c r="S56" t="n">
-        <v>2.84</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="57">
@@ -3787,7 +3787,7 @@
         <v>19</v>
       </c>
       <c r="B57" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C57" t="n">
         <v>3</v>
@@ -3796,57 +3796,57 @@
         <v>0.6</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="I57" t="n">
-        <v>6.1</v>
+        <v>9.3</v>
       </c>
       <c r="J57" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="K57" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="L57" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="M57" t="n">
-        <v>3.45</v>
+        <v>1.66</v>
       </c>
       <c r="N57" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O57" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>6.4</v>
+        <v>3.74</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.1</v>
+        <v>10.9</v>
       </c>
       <c r="R57" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="S57" t="n">
-        <v>6.2</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B58" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C58" t="n">
         <v>3</v>
@@ -3855,57 +3855,57 @@
         <v>0.6</v>
       </c>
       <c r="E58" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G58" t="n">
         <v>4</v>
       </c>
       <c r="H58" t="n">
-        <v>38.3</v>
+        <v>6.4</v>
       </c>
       <c r="I58" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>3.42</v>
+        <v>6.38</v>
       </c>
       <c r="K58" t="n">
-        <v>16.2</v>
+        <v>15.2</v>
       </c>
       <c r="L58" t="n">
-        <v>1.6</v>
+        <v>7.3</v>
       </c>
       <c r="M58" t="n">
-        <v>0.76</v>
+        <v>4.84</v>
       </c>
       <c r="N58" t="n">
-        <v>11</v>
+        <v>2.9</v>
       </c>
       <c r="O58" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="P58" t="n">
-        <v>0.04</v>
+        <v>1.18</v>
       </c>
       <c r="Q58" t="n">
-        <v>10.6</v>
+        <v>0.8</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B59" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C59" t="n">
         <v>3</v>
@@ -3914,57 +3914,57 @@
         <v>0.6</v>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G59" t="n">
         <v>3</v>
       </c>
       <c r="H59" t="n">
-        <v>18.2</v>
+        <v>3.9</v>
       </c>
       <c r="I59" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J59" t="n">
-        <v>3.61</v>
+        <v>5.49</v>
       </c>
       <c r="K59" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="L59" t="n">
-        <v>6.7</v>
+        <v>9.7</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>6.32</v>
       </c>
       <c r="N59" t="n">
-        <v>10.7</v>
+        <v>8.1</v>
       </c>
       <c r="O59" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="P59" t="n">
-        <v>0.71</v>
+        <v>2.53</v>
       </c>
       <c r="Q59" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="R59" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S59" t="n">
-        <v>0.04</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B60" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C60" t="n">
         <v>3</v>
@@ -3973,57 +3973,57 @@
         <v>0.6</v>
       </c>
       <c r="E60" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G60" t="n">
         <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>9.3</v>
+        <v>1.7</v>
       </c>
       <c r="I60" t="n">
-        <v>11.6</v>
+        <v>7.2</v>
       </c>
       <c r="J60" t="n">
-        <v>3.82</v>
+        <v>4.26</v>
       </c>
       <c r="K60" t="n">
-        <v>9.1</v>
+        <v>2.5</v>
       </c>
       <c r="L60" t="n">
-        <v>9.3</v>
+        <v>7.3</v>
       </c>
       <c r="M60" t="n">
-        <v>3.82</v>
+        <v>4.52</v>
       </c>
       <c r="N60" t="n">
-        <v>10.1</v>
+        <v>28.1</v>
       </c>
       <c r="O60" t="n">
-        <v>7</v>
+        <v>11.2</v>
       </c>
       <c r="P60" t="n">
-        <v>3</v>
+        <v>7.01</v>
       </c>
       <c r="Q60" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="R60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S60" t="n">
-        <v>0.9</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B61" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C61" t="n">
         <v>3</v>
@@ -4032,49 +4032,49 @@
         <v>0.6</v>
       </c>
       <c r="E61" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="I61" t="n">
-        <v>10.7</v>
+        <v>5.8</v>
       </c>
       <c r="J61" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="K61" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="L61" t="n">
-        <v>10.4</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>1.13</v>
       </c>
       <c r="N61" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="O61" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="P61" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="Q61" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="R61" t="n">
-        <v>8.2</v>
+        <v>11.6</v>
       </c>
       <c r="S61" t="n">
-        <v>2.93</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="62">
@@ -4082,7 +4082,7 @@
         <v>20</v>
       </c>
       <c r="B62" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C62" t="n">
         <v>3</v>
@@ -4091,49 +4091,49 @@
         <v>0.6</v>
       </c>
       <c r="E62" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G62" t="n">
         <v>4</v>
       </c>
       <c r="H62" t="n">
-        <v>40.6</v>
+        <v>12.4</v>
       </c>
       <c r="I62" t="n">
-        <v>10.6</v>
+        <v>7.1</v>
       </c>
       <c r="J62" t="n">
-        <v>6.83</v>
+        <v>3.11</v>
       </c>
       <c r="K62" t="n">
-        <v>10.8</v>
+        <v>14.4</v>
       </c>
       <c r="L62" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M62" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="N62" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="O62" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R62" t="n">
         <v>0.1</v>
       </c>
-      <c r="P62" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="63">
@@ -4141,7 +4141,7 @@
         <v>20</v>
       </c>
       <c r="B63" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C63" t="n">
         <v>3</v>
@@ -4150,49 +4150,49 @@
         <v>0.6</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G63" t="n">
         <v>3</v>
       </c>
       <c r="H63" t="n">
-        <v>10.1</v>
+        <v>12.8</v>
       </c>
       <c r="I63" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="J63" t="n">
-        <v>5.36</v>
+        <v>3.73</v>
       </c>
       <c r="K63" t="n">
-        <v>31.4</v>
+        <v>21.4</v>
       </c>
       <c r="L63" t="n">
-        <v>9.8</v>
+        <v>6.2</v>
       </c>
       <c r="M63" t="n">
-        <v>6.37</v>
+        <v>2.76</v>
       </c>
       <c r="N63" t="n">
-        <v>7</v>
+        <v>9.3</v>
       </c>
       <c r="O63" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="P63" t="n">
-        <v>1.7</v>
+        <v>0.89</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="R63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S63" t="n">
         <v>0.2</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0.12</v>
       </c>
     </row>
     <row r="64">
@@ -4200,7 +4200,7 @@
         <v>20</v>
       </c>
       <c r="B64" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C64" t="n">
         <v>3</v>
@@ -4209,49 +4209,49 @@
         <v>0.6</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G64" t="n">
         <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>7.1</v>
       </c>
       <c r="I64" t="n">
-        <v>8.3</v>
+        <v>12.1</v>
       </c>
       <c r="J64" t="n">
-        <v>4.54</v>
+        <v>3.94</v>
       </c>
       <c r="K64" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="L64" t="n">
-        <v>9.7</v>
+        <v>7.9</v>
       </c>
       <c r="M64" t="n">
-        <v>6.06</v>
+        <v>3.17</v>
       </c>
       <c r="N64" t="n">
-        <v>6.9</v>
+        <v>23.6</v>
       </c>
       <c r="O64" t="n">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="P64" t="n">
-        <v>6</v>
+        <v>3.21</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="R64" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="S64" t="n">
-        <v>1.92</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="65">
@@ -4259,7 +4259,7 @@
         <v>20</v>
       </c>
       <c r="B65" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C65" t="n">
         <v>3</v>
@@ -4268,57 +4268,57 @@
         <v>0.6</v>
       </c>
       <c r="E65" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I65" t="n">
-        <v>6.8</v>
+        <v>10.3</v>
       </c>
       <c r="J65" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="K65" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="L65" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="M65" t="n">
-        <v>3.76</v>
+        <v>2.2</v>
       </c>
       <c r="N65" t="n">
-        <v>2.9</v>
+        <v>8.8</v>
       </c>
       <c r="O65" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="P65" t="n">
-        <v>7.29</v>
+        <v>4.44</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.2</v>
+        <v>13.6</v>
       </c>
       <c r="R65" t="n">
-        <v>8.8</v>
+        <v>9.6</v>
       </c>
       <c r="S65" t="n">
-        <v>5.07</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B66" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C66" t="n">
         <v>3</v>
@@ -4327,57 +4327,57 @@
         <v>0.6</v>
       </c>
       <c r="E66" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G66" t="n">
         <v>4</v>
       </c>
       <c r="H66" t="n">
-        <v>33.5</v>
+        <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="J66" t="n">
-        <v>3.59</v>
+        <v>5.64</v>
       </c>
       <c r="K66" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="L66" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="M66" t="n">
-        <v>0.74</v>
+        <v>3.96</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="P66" t="n">
-        <v>0.05</v>
+        <v>0.33</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B67" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C67" t="n">
         <v>3</v>
@@ -4386,57 +4386,57 @@
         <v>0.6</v>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
         <v>3</v>
       </c>
       <c r="H67" t="n">
-        <v>9.8</v>
+        <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="J67" t="n">
-        <v>3.93</v>
+        <v>5.91</v>
       </c>
       <c r="K67" t="n">
-        <v>23.8</v>
+        <v>19</v>
       </c>
       <c r="L67" t="n">
-        <v>6.8</v>
+        <v>8.2</v>
       </c>
       <c r="M67" t="n">
-        <v>3.09</v>
+        <v>5.22</v>
       </c>
       <c r="N67" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="O67" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="P67" t="n">
-        <v>0.69</v>
+        <v>2.16</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="S67" t="n">
-        <v>0.06</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B68" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C68" t="n">
         <v>3</v>
@@ -4445,57 +4445,57 @@
         <v>0.6</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G68" t="n">
         <v>2</v>
       </c>
       <c r="H68" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>9.1</v>
+        <v>8.8</v>
       </c>
       <c r="J68" t="n">
-        <v>3.88</v>
+        <v>4.92</v>
       </c>
       <c r="K68" t="n">
-        <v>8.3</v>
+        <v>4</v>
       </c>
       <c r="L68" t="n">
-        <v>9.8</v>
+        <v>6.9</v>
       </c>
       <c r="M68" t="n">
-        <v>4.26</v>
+        <v>4.14</v>
       </c>
       <c r="N68" t="n">
-        <v>12.2</v>
+        <v>39</v>
       </c>
       <c r="O68" t="n">
-        <v>9.7</v>
+        <v>11.9</v>
       </c>
       <c r="P68" t="n">
-        <v>4.28</v>
+        <v>7.14</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="R68" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="S68" t="n">
-        <v>1.28</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B69" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C69" t="n">
         <v>3</v>
@@ -4504,49 +4504,49 @@
         <v>0.6</v>
       </c>
       <c r="E69" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>8.1</v>
+        <v>5.8</v>
       </c>
       <c r="J69" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="K69" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>9.7</v>
+        <v>2.5</v>
       </c>
       <c r="M69" t="n">
-        <v>4.11</v>
+        <v>1.29</v>
       </c>
       <c r="N69" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="O69" t="n">
-        <v>11.6</v>
+        <v>10.2</v>
       </c>
       <c r="P69" t="n">
-        <v>4.96</v>
+        <v>5.79</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="R69" t="n">
         <v>12.1</v>
       </c>
       <c r="S69" t="n">
-        <v>5.13</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="70">
@@ -4554,7 +4554,7 @@
         <v>21</v>
       </c>
       <c r="B70" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C70" t="n">
         <v>3</v>
@@ -4563,49 +4563,49 @@
         <v>0.6</v>
       </c>
       <c r="E70" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G70" t="n">
         <v>4</v>
       </c>
       <c r="H70" t="n">
-        <v>40.3</v>
+        <v>9</v>
       </c>
       <c r="I70" t="n">
-        <v>10.6</v>
+        <v>7.5</v>
       </c>
       <c r="J70" t="n">
-        <v>6.93</v>
+        <v>3.3</v>
       </c>
       <c r="K70" t="n">
-        <v>8.3</v>
+        <v>13</v>
       </c>
       <c r="L70" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="M70" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="N70" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="P70" t="n">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="71">
@@ -4613,7 +4613,7 @@
         <v>21</v>
       </c>
       <c r="B71" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C71" t="n">
         <v>3</v>
@@ -4622,49 +4622,49 @@
         <v>0.6</v>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G71" t="n">
         <v>3</v>
       </c>
       <c r="H71" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="I71" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J71" t="n">
-        <v>5.54</v>
+        <v>3.72</v>
       </c>
       <c r="K71" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="L71" t="n">
-        <v>9.2</v>
+        <v>7.5</v>
       </c>
       <c r="M71" t="n">
-        <v>6.04</v>
+        <v>3.3</v>
       </c>
       <c r="N71" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="O71" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="P71" t="n">
-        <v>1.39</v>
+        <v>0.72</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="S71" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="72">
@@ -4672,7 +4672,7 @@
         <v>21</v>
       </c>
       <c r="B72" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C72" t="n">
         <v>3</v>
@@ -4681,49 +4681,49 @@
         <v>0.6</v>
       </c>
       <c r="E72" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G72" t="n">
         <v>2</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>7.2</v>
+        <v>9.1</v>
       </c>
       <c r="J72" t="n">
-        <v>4.67</v>
+        <v>3.84</v>
       </c>
       <c r="K72" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="L72" t="n">
-        <v>9.2</v>
+        <v>8.9</v>
       </c>
       <c r="M72" t="n">
-        <v>6</v>
+        <v>3.84</v>
       </c>
       <c r="N72" t="n">
-        <v>6.1</v>
+        <v>28</v>
       </c>
       <c r="O72" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="P72" t="n">
-        <v>7.02</v>
+        <v>4.59</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="R72" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="S72" t="n">
-        <v>2.39</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="73">
@@ -4731,7 +4731,7 @@
         <v>21</v>
       </c>
       <c r="B73" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C73" t="n">
         <v>3</v>
@@ -4740,57 +4740,57 @@
         <v>0.6</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>5.7</v>
+        <v>8.2</v>
       </c>
       <c r="J73" t="n">
-        <v>3.71</v>
+        <v>3.51</v>
       </c>
       <c r="K73" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="L73" t="n">
         <v>7.6</v>
       </c>
       <c r="M73" t="n">
-        <v>4.93</v>
+        <v>3.21</v>
       </c>
       <c r="N73" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="O73" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>6.56</v>
+        <v>4.2</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="R73" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="S73" t="n">
-        <v>7.99</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B74" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C74" t="n">
         <v>3</v>
@@ -4799,57 +4799,57 @@
         <v>0.6</v>
       </c>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G74" t="n">
         <v>4</v>
       </c>
       <c r="H74" t="n">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="I74" t="n">
-        <v>8.1</v>
+        <v>10.5</v>
       </c>
       <c r="J74" t="n">
-        <v>3.6</v>
+        <v>6.69</v>
       </c>
       <c r="K74" t="n">
-        <v>13.1</v>
+        <v>10</v>
       </c>
       <c r="L74" t="n">
-        <v>4.6</v>
+        <v>6.1</v>
       </c>
       <c r="M74" t="n">
-        <v>2.14</v>
+        <v>4.11</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="P74" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B75" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C75" t="n">
         <v>3</v>
@@ -4858,57 +4858,57 @@
         <v>0.6</v>
       </c>
       <c r="E75" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
         <v>3</v>
       </c>
       <c r="H75" t="n">
-        <v>8.6</v>
+        <v>3</v>
       </c>
       <c r="I75" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="J75" t="n">
-        <v>4.14</v>
+        <v>5.58</v>
       </c>
       <c r="K75" t="n">
-        <v>20.4</v>
+        <v>27</v>
       </c>
       <c r="L75" t="n">
-        <v>7.4</v>
+        <v>9.3</v>
       </c>
       <c r="M75" t="n">
-        <v>3.36</v>
+        <v>6.12</v>
       </c>
       <c r="N75" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="O75" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="P75" t="n">
-        <v>1.05</v>
+        <v>1.71</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="R75" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.24</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B76" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C76" t="n">
         <v>3</v>
@@ -4917,57 +4917,57 @@
         <v>0.6</v>
       </c>
       <c r="E76" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G76" t="n">
         <v>2</v>
       </c>
       <c r="H76" t="n">
+        <v>5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
+      <c r="L76" t="n">
+        <v>8.8</v>
+      </c>
+      <c r="M76" t="n">
         <v>5.4</v>
       </c>
-      <c r="I76" t="n">
+      <c r="N76" t="n">
+        <v>31</v>
+      </c>
+      <c r="O76" t="n">
         <v>10.6</v>
       </c>
-      <c r="J76" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="K76" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L76" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M76" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="N76" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="O76" t="n">
-        <v>9.3</v>
-      </c>
       <c r="P76" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="R76" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="S76" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B77" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C77" t="n">
         <v>3</v>
@@ -4976,49 +4976,49 @@
         <v>0.6</v>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F77" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3</v>
+      </c>
+      <c r="O77" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="P77" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>4</v>
+      </c>
+      <c r="R77" t="n">
         <v>9.3</v>
       </c>
-      <c r="J77" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="K77" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L77" t="n">
-        <v>5</v>
-      </c>
-      <c r="M77" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="N77" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O77" t="n">
-        <v>10</v>
-      </c>
-      <c r="P77" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="R77" t="n">
-        <v>10.3</v>
-      </c>
       <c r="S77" t="n">
-        <v>3.83</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="78">
@@ -5038,46 +5038,46 @@
         <v>9</v>
       </c>
       <c r="F78" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G78" t="n">
         <v>4</v>
       </c>
       <c r="H78" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I78" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="J78" t="n">
-        <v>6.38</v>
+        <v>7.11</v>
       </c>
       <c r="K78" t="n">
-        <v>15.2</v>
+        <v>21</v>
       </c>
       <c r="L78" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="M78" t="n">
-        <v>4.84</v>
+        <v>5.22</v>
       </c>
       <c r="N78" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="P78" t="n">
-        <v>1.18</v>
+        <v>0.57</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -5097,46 +5097,46 @@
         <v>9</v>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G79" t="n">
         <v>3</v>
       </c>
       <c r="H79" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="J79" t="n">
-        <v>5.49</v>
+        <v>5.43</v>
       </c>
       <c r="K79" t="n">
-        <v>25.8</v>
+        <v>32</v>
       </c>
       <c r="L79" t="n">
-        <v>9.7</v>
+        <v>10.5</v>
       </c>
       <c r="M79" t="n">
-        <v>6.32</v>
+        <v>7.11</v>
       </c>
       <c r="N79" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="O79" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="P79" t="n">
-        <v>2.53</v>
+        <v>1.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="S79" t="n">
-        <v>0.78</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="80">
@@ -5156,46 +5156,46 @@
         <v>9</v>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G80" t="n">
         <v>2</v>
       </c>
       <c r="H80" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="I80" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="J80" t="n">
-        <v>4.26</v>
+        <v>4.68</v>
       </c>
       <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="M80" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N80" t="n">
+        <v>31</v>
+      </c>
+      <c r="O80" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P80" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>4</v>
+      </c>
+      <c r="R80" t="n">
         <v>2.5</v>
       </c>
-      <c r="L80" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M80" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="N80" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="O80" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="P80" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>10</v>
-      </c>
-      <c r="R80" t="n">
-        <v>4</v>
-      </c>
       <c r="S80" t="n">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="81">
@@ -5215,54 +5215,54 @@
         <v>9</v>
       </c>
       <c r="F81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J81" t="n">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="K81" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="M81" t="n">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>7.8</v>
+        <v>9.3</v>
       </c>
       <c r="P81" t="n">
-        <v>4.69</v>
+        <v>5.79</v>
       </c>
       <c r="Q81" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="R81" t="n">
-        <v>11.6</v>
+        <v>9.1</v>
       </c>
       <c r="S81" t="n">
-        <v>6.92</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B82" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C82" t="n">
         <v>3</v>
@@ -5271,7 +5271,7 @@
         <v>0.6</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>6</v>
@@ -5280,48 +5280,48 @@
         <v>4</v>
       </c>
       <c r="H82" t="n">
-        <v>12.4</v>
+        <v>3</v>
       </c>
       <c r="I82" t="n">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="J82" t="n">
-        <v>3.11</v>
+        <v>5.52</v>
       </c>
       <c r="K82" t="n">
-        <v>14.4</v>
+        <v>17</v>
       </c>
       <c r="L82" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="M82" t="n">
-        <v>1.75</v>
+        <v>5.28</v>
       </c>
       <c r="N82" t="n">
-        <v>7.7</v>
+        <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="P82" t="n">
-        <v>0.33</v>
+        <v>0.96</v>
       </c>
       <c r="Q82" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B83" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C83" t="n">
         <v>3</v>
@@ -5330,7 +5330,7 @@
         <v>0.6</v>
       </c>
       <c r="E83" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F83" t="n">
         <v>6</v>
@@ -5339,48 +5339,48 @@
         <v>3</v>
       </c>
       <c r="H83" t="n">
-        <v>12.8</v>
+        <v>3</v>
       </c>
       <c r="I83" t="n">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="J83" t="n">
-        <v>3.73</v>
+        <v>5.31</v>
       </c>
       <c r="K83" t="n">
-        <v>21.4</v>
+        <v>34</v>
       </c>
       <c r="L83" t="n">
-        <v>6.2</v>
+        <v>12.3</v>
       </c>
       <c r="M83" t="n">
-        <v>2.76</v>
+        <v>7.65</v>
       </c>
       <c r="N83" t="n">
-        <v>9.3</v>
+        <v>4</v>
       </c>
       <c r="O83" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="P83" t="n">
-        <v>0.89</v>
+        <v>2.07</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="S83" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B84" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C84" t="n">
         <v>3</v>
@@ -5389,7 +5389,7 @@
         <v>0.6</v>
       </c>
       <c r="E84" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F84" t="n">
         <v>6</v>
@@ -5398,48 +5398,48 @@
         <v>2</v>
       </c>
       <c r="H84" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>12.1</v>
+        <v>6.8</v>
       </c>
       <c r="J84" t="n">
-        <v>3.94</v>
+        <v>4.26</v>
       </c>
       <c r="K84" t="n">
-        <v>8.6</v>
+        <v>2</v>
       </c>
       <c r="L84" t="n">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="M84" t="n">
-        <v>3.17</v>
+        <v>3.57</v>
       </c>
       <c r="N84" t="n">
-        <v>23.6</v>
+        <v>29</v>
       </c>
       <c r="O84" t="n">
-        <v>7.7</v>
+        <v>11</v>
       </c>
       <c r="P84" t="n">
-        <v>3.21</v>
+        <v>6.99</v>
       </c>
       <c r="Q84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R84" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="S84" t="n">
-        <v>0.88</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B85" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C85" t="n">
         <v>3</v>
@@ -5448,7 +5448,7 @@
         <v>0.6</v>
       </c>
       <c r="E85" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F85" t="n">
         <v>6</v>
@@ -5457,45 +5457,45 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>10.3</v>
+        <v>5.5</v>
       </c>
       <c r="J85" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
         <v>3.4</v>
       </c>
-      <c r="K85" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L85" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M85" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="N85" t="n">
-        <v>8.8</v>
+        <v>3</v>
       </c>
       <c r="O85" t="n">
-        <v>12.8</v>
+        <v>8.1</v>
       </c>
       <c r="P85" t="n">
-        <v>4.44</v>
+        <v>4.98</v>
       </c>
       <c r="Q85" t="n">
-        <v>13.6</v>
+        <v>4</v>
       </c>
       <c r="R85" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="S85" t="n">
-        <v>3.45</v>
+        <v>8.37</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B86" t="n">
         <v>72</v>
@@ -5510,51 +5510,51 @@
         <v>9</v>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G86" t="n">
         <v>4</v>
       </c>
       <c r="H86" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I86" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J86" t="n">
-        <v>6.01</v>
+        <v>6.93</v>
       </c>
       <c r="K86" t="n">
-        <v>13.2</v>
+        <v>34</v>
       </c>
       <c r="L86" t="n">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="M86" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N86" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="O86" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="P86" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B87" t="n">
         <v>72</v>
@@ -5569,40 +5569,40 @@
         <v>9</v>
       </c>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G87" t="n">
         <v>3</v>
       </c>
       <c r="H87" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>9.7</v>
+        <v>7.7</v>
       </c>
       <c r="J87" t="n">
-        <v>5.63</v>
+        <v>5.22</v>
       </c>
       <c r="K87" t="n">
-        <v>25.4</v>
+        <v>6</v>
       </c>
       <c r="L87" t="n">
-        <v>8.7</v>
+        <v>8.9</v>
       </c>
       <c r="M87" t="n">
-        <v>5.59</v>
+        <v>6.15</v>
       </c>
       <c r="N87" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="O87" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="P87" t="n">
-        <v>2.1</v>
+        <v>4.92</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0.6</v>
@@ -5613,7 +5613,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B88" t="n">
         <v>72</v>
@@ -5628,51 +5628,51 @@
         <v>9</v>
       </c>
       <c r="F88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G88" t="n">
         <v>2</v>
       </c>
       <c r="H88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>8.1</v>
+        <v>5.7</v>
       </c>
       <c r="J88" t="n">
-        <v>4.48</v>
+        <v>3.9</v>
       </c>
       <c r="K88" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="L88" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M88" t="n">
-        <v>4.36</v>
+        <v>4.86</v>
       </c>
       <c r="N88" t="n">
-        <v>30.9</v>
+        <v>4</v>
       </c>
       <c r="O88" t="n">
-        <v>11.3</v>
+        <v>10.4</v>
       </c>
       <c r="P88" t="n">
-        <v>6.92</v>
+        <v>7.08</v>
       </c>
       <c r="Q88" t="n">
-        <v>9.9</v>
+        <v>20</v>
       </c>
       <c r="R88" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="S88" t="n">
-        <v>2.08</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B89" t="n">
         <v>72</v>
@@ -5687,46 +5687,46 @@
         <v>9</v>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="K89" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="M89" t="n">
-        <v>1.45</v>
+        <v>3.66</v>
       </c>
       <c r="N89" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O89" t="n">
-        <v>10.7</v>
+        <v>6.5</v>
       </c>
       <c r="P89" t="n">
-        <v>6.18</v>
+        <v>4.41</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="R89" t="n">
-        <v>11.4</v>
+        <v>9.9</v>
       </c>
       <c r="S89" t="n">
-        <v>6.58</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="90">
@@ -5746,46 +5746,46 @@
         <v>6</v>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G90" t="n">
         <v>4</v>
       </c>
       <c r="H90" t="n">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="I90" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="J90" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="K90" t="n">
-        <v>8.7</v>
+        <v>9</v>
       </c>
       <c r="L90" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="M90" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="N90" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="P90" t="n">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5805,46 +5805,46 @@
         <v>6</v>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G91" t="n">
         <v>3</v>
       </c>
       <c r="H91" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="I91" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="J91" t="n">
-        <v>3.97</v>
+        <v>3.75</v>
       </c>
       <c r="K91" t="n">
-        <v>27.2</v>
+        <v>24</v>
       </c>
       <c r="L91" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="M91" t="n">
-        <v>4.04</v>
+        <v>3.84</v>
       </c>
       <c r="N91" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="O91" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="P91" t="n">
-        <v>1.16</v>
+        <v>0.87</v>
       </c>
       <c r="Q91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5864,46 +5864,46 @@
         <v>6</v>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G92" t="n">
         <v>2</v>
       </c>
       <c r="H92" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>8.9</v>
+        <v>9.7</v>
       </c>
       <c r="J92" t="n">
-        <v>3.82</v>
+        <v>4.14</v>
       </c>
       <c r="K92" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L92" t="n">
-        <v>8.3</v>
+        <v>8.7</v>
       </c>
       <c r="M92" t="n">
-        <v>3.64</v>
+        <v>3.84</v>
       </c>
       <c r="N92" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O92" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="P92" t="n">
-        <v>4.67</v>
+        <v>5.13</v>
       </c>
       <c r="Q92" t="n">
-        <v>7.3</v>
+        <v>4</v>
       </c>
       <c r="R92" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S92" t="n">
-        <v>1.2</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="93">
@@ -5923,46 +5923,46 @@
         <v>6</v>
       </c>
       <c r="F93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>7.9</v>
+        <v>8.2</v>
       </c>
       <c r="J93" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="K93" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="L93" t="n">
-        <v>7.2</v>
+        <v>8.8</v>
       </c>
       <c r="M93" t="n">
-        <v>3.07</v>
+        <v>3.78</v>
       </c>
       <c r="N93" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>9.2</v>
+        <v>10.1</v>
       </c>
       <c r="P93" t="n">
-        <v>3.92</v>
+        <v>4.38</v>
       </c>
       <c r="Q93" t="n">
-        <v>10.7</v>
+        <v>7</v>
       </c>
       <c r="R93" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="S93" t="n">
-        <v>5.17</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="94">
@@ -5982,46 +5982,46 @@
         <v>9</v>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G94" t="n">
         <v>4</v>
       </c>
       <c r="H94" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I94" t="n">
-        <v>9.2</v>
+        <v>10.5</v>
       </c>
       <c r="J94" t="n">
-        <v>5.95</v>
+        <v>6.93</v>
       </c>
       <c r="K94" t="n">
-        <v>13.7</v>
+        <v>9</v>
       </c>
       <c r="L94" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="M94" t="n">
-        <v>4.03</v>
+        <v>3.9</v>
       </c>
       <c r="N94" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O94" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="P94" t="n">
-        <v>0.73</v>
+        <v>0.3</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -6041,46 +6041,46 @@
         <v>9</v>
       </c>
       <c r="F95" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G95" t="n">
         <v>3</v>
       </c>
       <c r="H95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
-        <v>5.66</v>
+        <v>6.15</v>
       </c>
       <c r="K95" t="n">
-        <v>28.5</v>
+        <v>21</v>
       </c>
       <c r="L95" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M95" t="n">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="N95" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="O95" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="P95" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="Q95" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="S95" t="n">
-        <v>0.48</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="96">
@@ -6100,46 +6100,46 @@
         <v>9</v>
       </c>
       <c r="F96" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G96" t="n">
         <v>2</v>
       </c>
       <c r="H96" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>7.2</v>
       </c>
       <c r="J96" t="n">
-        <v>4.55</v>
+        <v>4.68</v>
       </c>
       <c r="K96" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="L96" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="M96" t="n">
-        <v>4.14</v>
+        <v>5.16</v>
       </c>
       <c r="N96" t="n">
-        <v>32.3</v>
+        <v>41</v>
       </c>
       <c r="O96" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="P96" t="n">
-        <v>7.37</v>
+        <v>7.98</v>
       </c>
       <c r="Q96" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="R96" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S96" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="97">
@@ -6159,7 +6159,7 @@
         <v>9</v>
       </c>
       <c r="F97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G97" t="n">
         <v>1</v>
@@ -6168,37 +6168,37 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J97" t="n">
-        <v>3.51</v>
+        <v>3.63</v>
       </c>
       <c r="K97" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="M97" t="n">
-        <v>2.88</v>
+        <v>4.23</v>
       </c>
       <c r="N97" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="P97" t="n">
-        <v>4.72</v>
+        <v>4.98</v>
       </c>
       <c r="Q97" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R97" t="n">
-        <v>13.1</v>
+        <v>12.2</v>
       </c>
       <c r="S97" t="n">
-        <v>8.16</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -6475,36 +6475,36 @@
         <v>0.6</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>71.6</v>
+        <v>50.4</v>
       </c>
       <c r="H7" t="n">
-        <v>69</v>
+        <v>40.4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.37</v>
+        <v>8.85</v>
       </c>
       <c r="J7" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="M7" t="n">
-        <v>20.4</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>48</v>
@@ -6522,25 +6522,25 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>50.4</v>
+        <v>51.3</v>
       </c>
       <c r="H8" t="n">
-        <v>40.4</v>
+        <v>37.3</v>
       </c>
       <c r="I8" t="n">
-        <v>8.85</v>
+        <v>10.04</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L8" t="n">
         <v>48</v>
       </c>
       <c r="M8" t="n">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="9">
@@ -6548,7 +6548,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -6557,39 +6557,39 @@
         <v>0.6</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>59.9</v>
+        <v>59.7</v>
       </c>
       <c r="H9" t="n">
-        <v>64.1</v>
+        <v>40.1</v>
       </c>
       <c r="I9" t="n">
-        <v>9.76</v>
+        <v>9.1</v>
       </c>
       <c r="J9" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="L9" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="M9" t="n">
-        <v>21.6</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -6598,31 +6598,31 @@
         <v>0.6</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>51.3</v>
+        <v>71.6</v>
       </c>
       <c r="H10" t="n">
-        <v>37.3</v>
+        <v>63.5</v>
       </c>
       <c r="I10" t="n">
-        <v>10.04</v>
+        <v>9.57</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="L10" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="M10" t="n">
-        <v>13.6</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="11">
@@ -6630,7 +6630,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
@@ -6639,39 +6639,39 @@
         <v>0.6</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>57.3</v>
+        <v>63.7</v>
       </c>
       <c r="H11" t="n">
-        <v>61.1</v>
+        <v>37.6</v>
       </c>
       <c r="I11" t="n">
-        <v>11.49</v>
+        <v>9.69</v>
       </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="M11" t="n">
-        <v>19.4</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
@@ -6680,31 +6680,31 @@
         <v>0.6</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>60.5</v>
+        <v>72</v>
       </c>
       <c r="H12" t="n">
-        <v>43.7</v>
+        <v>60.3</v>
       </c>
       <c r="I12" t="n">
-        <v>4.54</v>
+        <v>11.44</v>
       </c>
       <c r="J12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="M12" t="n">
-        <v>18.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="13">
@@ -6712,7 +6712,7 @@
         <v>21</v>
       </c>
       <c r="B13" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
@@ -6721,39 +6721,39 @@
         <v>0.6</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>66</v>
+        <v>57.3</v>
       </c>
       <c r="H13" t="n">
-        <v>65.3</v>
+        <v>43.5</v>
       </c>
       <c r="I13" t="n">
-        <v>6.22</v>
+        <v>4.64</v>
       </c>
       <c r="J13" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K13" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="L13" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="M13" t="n">
-        <v>22.2</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
@@ -6762,31 +6762,31 @@
         <v>0.6</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>59.7</v>
+        <v>70.1</v>
       </c>
       <c r="H14" t="n">
-        <v>40.1</v>
+        <v>65.2</v>
       </c>
       <c r="I14" t="n">
-        <v>9.1</v>
+        <v>6.08</v>
       </c>
       <c r="J14" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="K14" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="L14" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="M14" t="n">
-        <v>16.8</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="15">
@@ -6794,7 +6794,7 @@
         <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -6803,39 +6803,39 @@
         <v>0.6</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>71.6</v>
+        <v>48</v>
       </c>
       <c r="H15" t="n">
-        <v>63.5</v>
+        <v>40.2</v>
       </c>
       <c r="I15" t="n">
-        <v>9.57</v>
+        <v>8.69</v>
       </c>
       <c r="J15" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K15" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="L15" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="M15" t="n">
-        <v>22.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
@@ -6844,31 +6844,31 @@
         <v>0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>63.7</v>
+        <v>53.9</v>
       </c>
       <c r="H16" t="n">
-        <v>37.6</v>
+        <v>62.4</v>
       </c>
       <c r="I16" t="n">
-        <v>9.69</v>
+        <v>10.01</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="L16" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="M16" t="n">
-        <v>14.5</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="17">
@@ -6876,7 +6876,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
@@ -6885,39 +6885,39 @@
         <v>0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="H17" t="n">
-        <v>60.3</v>
+        <v>37.5</v>
       </c>
       <c r="I17" t="n">
-        <v>11.44</v>
+        <v>9.53</v>
       </c>
       <c r="J17" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L17" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="M17" t="n">
-        <v>20.4</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C18" t="n">
         <v>3</v>
@@ -6926,31 +6926,31 @@
         <v>0.6</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>57.3</v>
+        <v>58</v>
       </c>
       <c r="H18" t="n">
-        <v>43.5</v>
+        <v>59.7</v>
       </c>
       <c r="I18" t="n">
-        <v>4.64</v>
+        <v>10.54</v>
       </c>
       <c r="J18" t="n">
         <v>24</v>
       </c>
       <c r="K18" t="n">
-        <v>45</v>
+        <v>61.5</v>
       </c>
       <c r="L18" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="M18" t="n">
-        <v>14.9</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="19">
@@ -6958,7 +6958,7 @@
         <v>21</v>
       </c>
       <c r="B19" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C19" t="n">
         <v>3</v>
@@ -6967,39 +6967,39 @@
         <v>0.6</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>70.1</v>
+        <v>57</v>
       </c>
       <c r="H19" t="n">
-        <v>65.2</v>
+        <v>43.2</v>
       </c>
       <c r="I19" t="n">
-        <v>6.08</v>
+        <v>4.35</v>
       </c>
       <c r="J19" t="n">
+        <v>27</v>
+      </c>
+      <c r="K19" t="n">
         <v>45</v>
       </c>
-      <c r="K19" t="n">
-        <v>66</v>
-      </c>
       <c r="L19" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="M19" t="n">
-        <v>19.8</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
@@ -7008,31 +7008,31 @@
         <v>0.6</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H20" t="n">
-        <v>40.2</v>
+        <v>60.8</v>
       </c>
       <c r="I20" t="n">
-        <v>8.69</v>
+        <v>11.69</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K20" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="L20" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="M20" t="n">
-        <v>16.7</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="21">
@@ -7052,36 +7052,36 @@
         <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>53.9</v>
+        <v>63</v>
       </c>
       <c r="H21" t="n">
-        <v>62.4</v>
+        <v>64.6</v>
       </c>
       <c r="I21" t="n">
-        <v>10.01</v>
+        <v>9.76</v>
       </c>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K21" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L21" t="n">
         <v>72</v>
       </c>
       <c r="M21" t="n">
-        <v>20.9</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
@@ -7090,36 +7090,36 @@
         <v>0.6</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="H22" t="n">
-        <v>37.5</v>
+        <v>63.2</v>
       </c>
       <c r="I22" t="n">
-        <v>9.53</v>
+        <v>6.75</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="K22" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="L22" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="M22" t="n">
-        <v>13.9</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="n">
         <v>72</v>
@@ -7134,28 +7134,28 @@
         <v>9</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>56.3</v>
+        <v>78</v>
       </c>
       <c r="H23" t="n">
-        <v>60.2</v>
+        <v>68.2</v>
       </c>
       <c r="I23" t="n">
-        <v>10.8</v>
+        <v>4.84</v>
       </c>
       <c r="J23" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="K23" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="L23" t="n">
         <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>20</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="24">
@@ -7175,16 +7175,16 @@
         <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>60.2</v>
+        <v>61</v>
       </c>
       <c r="H24" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
       <c r="I24" t="n">
-        <v>4.43</v>
+        <v>4.32</v>
       </c>
       <c r="J24" t="n">
         <v>27</v>
@@ -7196,7 +7196,7 @@
         <v>48</v>
       </c>
       <c r="M24" t="n">
-        <v>19.7</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="25">
@@ -7216,28 +7216,28 @@
         <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>60.8</v>
+        <v>62</v>
       </c>
       <c r="H25" t="n">
-        <v>63.7</v>
+        <v>65.2</v>
       </c>
       <c r="I25" t="n">
-        <v>6.36</v>
+        <v>6.31</v>
       </c>
       <c r="J25" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="K25" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L25" t="n">
         <v>72</v>
       </c>
       <c r="M25" t="n">
-        <v>22.7</v>
+        <v>21.8</v>
       </c>
     </row>
   </sheetData>
